--- a/excel/25000(n)/RAW_Dataset.xlsx
+++ b/excel/25000(n)/RAW_Dataset.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\#Java-Practice\##SS2\Lab3 Sorting\excel\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t xml:space="preserve">Algorithm </t>
   </si>
@@ -58,12 +58,166 @@
   </si>
   <si>
     <t>Trial 9</t>
+  </si>
+  <si>
+    <t>Bubble Sort</t>
+  </si>
+  <si>
+    <t>Bubble Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Insertion Sort</t>
+  </si>
+  <si>
+    <t>Insertion Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Selection Sort</t>
+  </si>
+  <si>
+    <t>Selection Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Merge Sort</t>
+  </si>
+  <si>
+    <t>Merge Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Quick Sort</t>
+  </si>
+  <si>
+    <t>Quick Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Trial 10</t>
+  </si>
+  <si>
+    <t>Trial 11</t>
+  </si>
+  <si>
+    <t>Trial 12</t>
+  </si>
+  <si>
+    <t>Trial 13</t>
+  </si>
+  <si>
+    <t>Trial 14</t>
+  </si>
+  <si>
+    <t>Trial 15</t>
+  </si>
+  <si>
+    <t>Trial 16</t>
+  </si>
+  <si>
+    <t>Trial 17</t>
+  </si>
+  <si>
+    <t>Trial 18</t>
+  </si>
+  <si>
+    <t>Trial 19</t>
+  </si>
+  <si>
+    <t>Trial 20</t>
+  </si>
+  <si>
+    <t>Trial 21</t>
+  </si>
+  <si>
+    <t>Trial 22</t>
+  </si>
+  <si>
+    <t>Trial 23</t>
+  </si>
+  <si>
+    <t>Trial 24</t>
+  </si>
+  <si>
+    <t>Trial 25</t>
+  </si>
+  <si>
+    <t>Trial 26</t>
+  </si>
+  <si>
+    <t>Trial 27</t>
+  </si>
+  <si>
+    <t>Trial 28</t>
+  </si>
+  <si>
+    <t>Trial 29</t>
+  </si>
+  <si>
+    <t>Trial 30</t>
+  </si>
+  <si>
+    <t>Trial 31</t>
+  </si>
+  <si>
+    <t>Trial 32</t>
+  </si>
+  <si>
+    <t>Trial 33</t>
+  </si>
+  <si>
+    <t>Trial 34</t>
+  </si>
+  <si>
+    <t>Trial 35</t>
+  </si>
+  <si>
+    <t>Trial 36</t>
+  </si>
+  <si>
+    <t>Trial 37</t>
+  </si>
+  <si>
+    <t>Trial 38</t>
+  </si>
+  <si>
+    <t>Trial 39</t>
+  </si>
+  <si>
+    <t>Trial 40</t>
+  </si>
+  <si>
+    <t>Trial 41</t>
+  </si>
+  <si>
+    <t>Trial 42</t>
+  </si>
+  <si>
+    <t>Trial 43</t>
+  </si>
+  <si>
+    <t>Trial 44</t>
+  </si>
+  <si>
+    <t>Trial 45</t>
+  </si>
+  <si>
+    <t>Trial 46</t>
+  </si>
+  <si>
+    <t>Trial 47</t>
+  </si>
+  <si>
+    <t>Trial 48</t>
+  </si>
+  <si>
+    <t>Trial 49</t>
+  </si>
+  <si>
+    <t>Trial 50</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -388,11 +542,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="14.77734375"/>
+    <col min="2" max="2" customWidth="true" width="13.33203125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.5">
@@ -402,32 +556,1735 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>10</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="P1" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="Q1" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="R1" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="S1" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="T1" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="U1" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="V1" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="W1" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="X1" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="Y1" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="Z1" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="AA1" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="AB1" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="AC1" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="AD1" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="AE1" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="AF1" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="AG1" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="AH1" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="AI1" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="AJ1" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="AK1" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="AL1" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="AM1" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="AN1" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="AO1" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="AP1" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="AQ1" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="AR1" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="AS1" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="AT1" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="AU1" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="AV1" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="AW1" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="AX1" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="AY1" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="AZ1" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B2" t="n" s="0">
+        <v>25000.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>6.523488E8</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>6.517144E8</v>
+      </c>
+      <c r="E2" t="n" s="0">
+        <v>6.356284E8</v>
+      </c>
+      <c r="F2" t="n" s="0">
+        <v>6.549012E8</v>
+      </c>
+      <c r="G2" t="n" s="0">
+        <v>6.732774E8</v>
+      </c>
+      <c r="H2" t="n" s="0">
+        <v>6.505755E8</v>
+      </c>
+      <c r="I2" t="n" s="0">
+        <v>6.50131E8</v>
+      </c>
+      <c r="J2" t="n" s="0">
+        <v>6.509592E8</v>
+      </c>
+      <c r="K2" t="n" s="0">
+        <v>6.434885E8</v>
+      </c>
+      <c r="L2" t="n" s="0">
+        <v>6.803847E8</v>
+      </c>
+      <c r="M2" t="n" s="0">
+        <v>6.407176E8</v>
+      </c>
+      <c r="N2" t="n" s="0">
+        <v>6.203529E8</v>
+      </c>
+      <c r="O2" t="n" s="0">
+        <v>6.296879E8</v>
+      </c>
+      <c r="P2" t="n" s="0">
+        <v>6.777557E8</v>
+      </c>
+      <c r="Q2" t="n" s="0">
+        <v>6.244359E8</v>
+      </c>
+      <c r="R2" t="n" s="0">
+        <v>6.254449E8</v>
+      </c>
+      <c r="S2" t="n" s="0">
+        <v>6.654437E8</v>
+      </c>
+      <c r="T2" t="n" s="0">
+        <v>6.618889E8</v>
+      </c>
+      <c r="U2" t="n" s="0">
+        <v>6.225721E8</v>
+      </c>
+      <c r="V2" t="n" s="0">
+        <v>6.425084E8</v>
+      </c>
+      <c r="W2" t="n" s="0">
+        <v>6.155316E8</v>
+      </c>
+      <c r="X2" t="n" s="0">
+        <v>6.192583E8</v>
+      </c>
+      <c r="Y2" t="n" s="0">
+        <v>6.982442E8</v>
+      </c>
+      <c r="Z2" t="n" s="0">
+        <v>6.21096E8</v>
+      </c>
+      <c r="AA2" t="n" s="0">
+        <v>6.293057E8</v>
+      </c>
+      <c r="AB2" t="n" s="0">
+        <v>6.342157E8</v>
+      </c>
+      <c r="AC2" t="n" s="0">
+        <v>6.331199E8</v>
+      </c>
+      <c r="AD2" t="n" s="0">
+        <v>6.411631E8</v>
+      </c>
+      <c r="AE2" t="n" s="0">
+        <v>6.375963E8</v>
+      </c>
+      <c r="AF2" t="n" s="0">
+        <v>7.030224E8</v>
+      </c>
+      <c r="AG2" t="n" s="0">
+        <v>6.230452E8</v>
+      </c>
+      <c r="AH2" t="n" s="0">
+        <v>6.755699E8</v>
+      </c>
+      <c r="AI2" t="n" s="0">
+        <v>6.650801E8</v>
+      </c>
+      <c r="AJ2" t="n" s="0">
+        <v>6.22137E8</v>
+      </c>
+      <c r="AK2" t="n" s="0">
+        <v>6.249415E8</v>
+      </c>
+      <c r="AL2" t="n" s="0">
+        <v>6.246032E8</v>
+      </c>
+      <c r="AM2" t="n" s="0">
+        <v>6.171262E8</v>
+      </c>
+      <c r="AN2" t="n" s="0">
+        <v>6.368553E8</v>
+      </c>
+      <c r="AO2" t="n" s="0">
+        <v>7.12107E8</v>
+      </c>
+      <c r="AP2" t="n" s="0">
+        <v>6.185437E8</v>
+      </c>
+      <c r="AQ2" t="n" s="0">
+        <v>6.372716E8</v>
+      </c>
+      <c r="AR2" t="n" s="0">
+        <v>6.238537E8</v>
+      </c>
+      <c r="AS2" t="n" s="0">
+        <v>6.181343E8</v>
+      </c>
+      <c r="AT2" t="n" s="0">
+        <v>6.356311E8</v>
+      </c>
+      <c r="AU2" t="n" s="0">
+        <v>6.175334E8</v>
+      </c>
+      <c r="AV2" t="n" s="0">
+        <v>6.23473E8</v>
+      </c>
+      <c r="AW2" t="n" s="0">
+        <v>6.491309E8</v>
+      </c>
+      <c r="AX2" t="n" s="0">
+        <v>6.184678E8</v>
+      </c>
+      <c r="AY2" t="n" s="0">
+        <v>6.25093E8</v>
+      </c>
+      <c r="AZ2" t="n" s="0">
+        <v>7.342325E8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B3" t="n" s="0">
+        <v>25000.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>6.560397E8</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>6.453364E8</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>6.305421E8</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>6.420923E8</v>
+      </c>
+      <c r="G3" t="n" s="0">
+        <v>6.720412E8</v>
+      </c>
+      <c r="H3" t="n" s="0">
+        <v>6.485384E8</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>6.44436E8</v>
+      </c>
+      <c r="J3" t="n" s="0">
+        <v>6.611834E8</v>
+      </c>
+      <c r="K3" t="n" s="0">
+        <v>6.450075E8</v>
+      </c>
+      <c r="L3" t="n" s="0">
+        <v>6.372588E8</v>
+      </c>
+      <c r="M3" t="n" s="0">
+        <v>6.215936E8</v>
+      </c>
+      <c r="N3" t="n" s="0">
+        <v>6.242595E8</v>
+      </c>
+      <c r="O3" t="n" s="0">
+        <v>6.218404E8</v>
+      </c>
+      <c r="P3" t="n" s="0">
+        <v>6.229136E8</v>
+      </c>
+      <c r="Q3" t="n" s="0">
+        <v>6.254406E8</v>
+      </c>
+      <c r="R3" t="n" s="0">
+        <v>6.170387E8</v>
+      </c>
+      <c r="S3" t="n" s="0">
+        <v>6.211607E8</v>
+      </c>
+      <c r="T3" t="n" s="0">
+        <v>6.177348E8</v>
+      </c>
+      <c r="U3" t="n" s="0">
+        <v>6.258346E8</v>
+      </c>
+      <c r="V3" t="n" s="0">
+        <v>6.209417E8</v>
+      </c>
+      <c r="W3" t="n" s="0">
+        <v>6.181288E8</v>
+      </c>
+      <c r="X3" t="n" s="0">
+        <v>6.178851E8</v>
+      </c>
+      <c r="Y3" t="n" s="0">
+        <v>6.20143E8</v>
+      </c>
+      <c r="Z3" t="n" s="0">
+        <v>6.268592E8</v>
+      </c>
+      <c r="AA3" t="n" s="0">
+        <v>6.199816E8</v>
+      </c>
+      <c r="AB3" t="n" s="0">
+        <v>6.130381E8</v>
+      </c>
+      <c r="AC3" t="n" s="0">
+        <v>6.154558E8</v>
+      </c>
+      <c r="AD3" t="n" s="0">
+        <v>6.514472E8</v>
+      </c>
+      <c r="AE3" t="n" s="0">
+        <v>6.178571E8</v>
+      </c>
+      <c r="AF3" t="n" s="0">
+        <v>6.216266E8</v>
+      </c>
+      <c r="AG3" t="n" s="0">
+        <v>6.206504E8</v>
+      </c>
+      <c r="AH3" t="n" s="0">
+        <v>6.63124E8</v>
+      </c>
+      <c r="AI3" t="n" s="0">
+        <v>6.636984E8</v>
+      </c>
+      <c r="AJ3" t="n" s="0">
+        <v>6.202633E8</v>
+      </c>
+      <c r="AK3" t="n" s="0">
+        <v>6.143538E8</v>
+      </c>
+      <c r="AL3" t="n" s="0">
+        <v>6.174206E8</v>
+      </c>
+      <c r="AM3" t="n" s="0">
+        <v>6.149037E8</v>
+      </c>
+      <c r="AN3" t="n" s="0">
+        <v>6.216758E8</v>
+      </c>
+      <c r="AO3" t="n" s="0">
+        <v>6.351208E8</v>
+      </c>
+      <c r="AP3" t="n" s="0">
+        <v>6.194094E8</v>
+      </c>
+      <c r="AQ3" t="n" s="0">
+        <v>6.18859E8</v>
+      </c>
+      <c r="AR3" t="n" s="0">
+        <v>6.258405E8</v>
+      </c>
+      <c r="AS3" t="n" s="0">
+        <v>6.175336E8</v>
+      </c>
+      <c r="AT3" t="n" s="0">
+        <v>6.234263E8</v>
+      </c>
+      <c r="AU3" t="n" s="0">
+        <v>6.13736E8</v>
+      </c>
+      <c r="AV3" t="n" s="0">
+        <v>6.382313E8</v>
+      </c>
+      <c r="AW3" t="n" s="0">
+        <v>6.161308E8</v>
+      </c>
+      <c r="AX3" t="n" s="0">
+        <v>6.163657E8</v>
+      </c>
+      <c r="AY3" t="n" s="0">
+        <v>6.148812E8</v>
+      </c>
+      <c r="AZ3" t="n" s="0">
+        <v>6.795472E8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>25000.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>8.49909E7</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>8.39356E7</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>8.25342E7</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>2.19678E7</v>
+      </c>
+      <c r="G4" t="n" s="0">
+        <v>2.1943E7</v>
+      </c>
+      <c r="H4" t="n" s="0">
+        <v>2.14488E7</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>2.21417E7</v>
+      </c>
+      <c r="J4" t="n" s="0">
+        <v>2.26103E7</v>
+      </c>
+      <c r="K4" t="n" s="0">
+        <v>2.25526E7</v>
+      </c>
+      <c r="L4" t="n" s="0">
+        <v>2.20491E7</v>
+      </c>
+      <c r="M4" t="n" s="0">
+        <v>2.17959E7</v>
+      </c>
+      <c r="N4" t="n" s="0">
+        <v>2.2205E7</v>
+      </c>
+      <c r="O4" t="n" s="0">
+        <v>2.28188E7</v>
+      </c>
+      <c r="P4" t="n" s="0">
+        <v>2.20602E7</v>
+      </c>
+      <c r="Q4" t="n" s="0">
+        <v>2.22723E7</v>
+      </c>
+      <c r="R4" t="n" s="0">
+        <v>2.19967E7</v>
+      </c>
+      <c r="S4" t="n" s="0">
+        <v>2.18859E7</v>
+      </c>
+      <c r="T4" t="n" s="0">
+        <v>2.19233E7</v>
+      </c>
+      <c r="U4" t="n" s="0">
+        <v>2.18778E7</v>
+      </c>
+      <c r="V4" t="n" s="0">
+        <v>2.21995E7</v>
+      </c>
+      <c r="W4" t="n" s="0">
+        <v>2.20875E7</v>
+      </c>
+      <c r="X4" t="n" s="0">
+        <v>2.17372E7</v>
+      </c>
+      <c r="Y4" t="n" s="0">
+        <v>2.19535E7</v>
+      </c>
+      <c r="Z4" t="n" s="0">
+        <v>2.24297E7</v>
+      </c>
+      <c r="AA4" t="n" s="0">
+        <v>2.23638E7</v>
+      </c>
+      <c r="AB4" t="n" s="0">
+        <v>2.19126E7</v>
+      </c>
+      <c r="AC4" t="n" s="0">
+        <v>2.17744E7</v>
+      </c>
+      <c r="AD4" t="n" s="0">
+        <v>2.17954E7</v>
+      </c>
+      <c r="AE4" t="n" s="0">
+        <v>2.14406E7</v>
+      </c>
+      <c r="AF4" t="n" s="0">
+        <v>2.22398E7</v>
+      </c>
+      <c r="AG4" t="n" s="0">
+        <v>2.18023E7</v>
+      </c>
+      <c r="AH4" t="n" s="0">
+        <v>2.32559E7</v>
+      </c>
+      <c r="AI4" t="n" s="0">
+        <v>2.30154E7</v>
+      </c>
+      <c r="AJ4" t="n" s="0">
+        <v>2.18829E7</v>
+      </c>
+      <c r="AK4" t="n" s="0">
+        <v>2.16004E7</v>
+      </c>
+      <c r="AL4" t="n" s="0">
+        <v>2.18696E7</v>
+      </c>
+      <c r="AM4" t="n" s="0">
+        <v>2.14172E7</v>
+      </c>
+      <c r="AN4" t="n" s="0">
+        <v>2.22442E7</v>
+      </c>
+      <c r="AO4" t="n" s="0">
+        <v>2.19019E7</v>
+      </c>
+      <c r="AP4" t="n" s="0">
+        <v>2.17809E7</v>
+      </c>
+      <c r="AQ4" t="n" s="0">
+        <v>2.20649E7</v>
+      </c>
+      <c r="AR4" t="n" s="0">
+        <v>2.17787E7</v>
+      </c>
+      <c r="AS4" t="n" s="0">
+        <v>2.22869E7</v>
+      </c>
+      <c r="AT4" t="n" s="0">
+        <v>2.17477E7</v>
+      </c>
+      <c r="AU4" t="n" s="0">
+        <v>2.18402E7</v>
+      </c>
+      <c r="AV4" t="n" s="0">
+        <v>2.20898E7</v>
+      </c>
+      <c r="AW4" t="n" s="0">
+        <v>2.30298E7</v>
+      </c>
+      <c r="AX4" t="n" s="0">
+        <v>2.18547E7</v>
+      </c>
+      <c r="AY4" t="n" s="0">
+        <v>2.12387E7</v>
+      </c>
+      <c r="AZ4" t="n" s="0">
+        <v>2.22516E7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>25000.0</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>8.49371E7</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>8.25083E7</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>8.30405E7</v>
+      </c>
+      <c r="F5" t="n" s="0">
+        <v>2.19713E7</v>
+      </c>
+      <c r="G5" t="n" s="0">
+        <v>2.18541E7</v>
+      </c>
+      <c r="H5" t="n" s="0">
+        <v>2.25137E7</v>
+      </c>
+      <c r="I5" t="n" s="0">
+        <v>2.21334E7</v>
+      </c>
+      <c r="J5" t="n" s="0">
+        <v>2.22423E7</v>
+      </c>
+      <c r="K5" t="n" s="0">
+        <v>2.30256E7</v>
+      </c>
+      <c r="L5" t="n" s="0">
+        <v>2.21923E7</v>
+      </c>
+      <c r="M5" t="n" s="0">
+        <v>2.21311E7</v>
+      </c>
+      <c r="N5" t="n" s="0">
+        <v>2.21036E7</v>
+      </c>
+      <c r="O5" t="n" s="0">
+        <v>2.22253E7</v>
+      </c>
+      <c r="P5" t="n" s="0">
+        <v>2.20433E7</v>
+      </c>
+      <c r="Q5" t="n" s="0">
+        <v>2.2352E7</v>
+      </c>
+      <c r="R5" t="n" s="0">
+        <v>2.14268E7</v>
+      </c>
+      <c r="S5" t="n" s="0">
+        <v>2.23168E7</v>
+      </c>
+      <c r="T5" t="n" s="0">
+        <v>2.27174E7</v>
+      </c>
+      <c r="U5" t="n" s="0">
+        <v>2.2379E7</v>
+      </c>
+      <c r="V5" t="n" s="0">
+        <v>2.17398E7</v>
+      </c>
+      <c r="W5" t="n" s="0">
+        <v>2.21335E7</v>
+      </c>
+      <c r="X5" t="n" s="0">
+        <v>2.26832E7</v>
+      </c>
+      <c r="Y5" t="n" s="0">
+        <v>2.18168E7</v>
+      </c>
+      <c r="Z5" t="n" s="0">
+        <v>2.19657E7</v>
+      </c>
+      <c r="AA5" t="n" s="0">
+        <v>2.22264E7</v>
+      </c>
+      <c r="AB5" t="n" s="0">
+        <v>2.15477E7</v>
+      </c>
+      <c r="AC5" t="n" s="0">
+        <v>2.17471E7</v>
+      </c>
+      <c r="AD5" t="n" s="0">
+        <v>2.29443E7</v>
+      </c>
+      <c r="AE5" t="n" s="0">
+        <v>2.13755E7</v>
+      </c>
+      <c r="AF5" t="n" s="0">
+        <v>2.18999E7</v>
+      </c>
+      <c r="AG5" t="n" s="0">
+        <v>2.20027E7</v>
+      </c>
+      <c r="AH5" t="n" s="0">
+        <v>2.33726E7</v>
+      </c>
+      <c r="AI5" t="n" s="0">
+        <v>2.31541E7</v>
+      </c>
+      <c r="AJ5" t="n" s="0">
+        <v>2.20925E7</v>
+      </c>
+      <c r="AK5" t="n" s="0">
+        <v>2.1474E7</v>
+      </c>
+      <c r="AL5" t="n" s="0">
+        <v>2.19405E7</v>
+      </c>
+      <c r="AM5" t="n" s="0">
+        <v>2.14046E7</v>
+      </c>
+      <c r="AN5" t="n" s="0">
+        <v>2.33488E7</v>
+      </c>
+      <c r="AO5" t="n" s="0">
+        <v>2.20689E7</v>
+      </c>
+      <c r="AP5" t="n" s="0">
+        <v>2.25912E7</v>
+      </c>
+      <c r="AQ5" t="n" s="0">
+        <v>2.20311E7</v>
+      </c>
+      <c r="AR5" t="n" s="0">
+        <v>2.21711E7</v>
+      </c>
+      <c r="AS5" t="n" s="0">
+        <v>2.21758E7</v>
+      </c>
+      <c r="AT5" t="n" s="0">
+        <v>2.29091E7</v>
+      </c>
+      <c r="AU5" t="n" s="0">
+        <v>2.20485E7</v>
+      </c>
+      <c r="AV5" t="n" s="0">
+        <v>2.19546E7</v>
+      </c>
+      <c r="AW5" t="n" s="0">
+        <v>2.21996E7</v>
+      </c>
+      <c r="AX5" t="n" s="0">
+        <v>2.17883E7</v>
+      </c>
+      <c r="AY5" t="n" s="0">
+        <v>2.16503E7</v>
+      </c>
+      <c r="AZ5" t="n" s="0">
+        <v>2.18011E7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>25000.0</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>1.480285E8</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>1.491018E8</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>1.034084E8</v>
+      </c>
+      <c r="F6" t="n" s="0">
+        <v>1.467535E8</v>
+      </c>
+      <c r="G6" t="n" s="0">
+        <v>1.465968E8</v>
+      </c>
+      <c r="H6" t="n" s="0">
+        <v>1.459322E8</v>
+      </c>
+      <c r="I6" t="n" s="0">
+        <v>1.466643E8</v>
+      </c>
+      <c r="J6" t="n" s="0">
+        <v>1.477477E8</v>
+      </c>
+      <c r="K6" t="n" s="0">
+        <v>1.469764E8</v>
+      </c>
+      <c r="L6" t="n" s="0">
+        <v>9.94927E7</v>
+      </c>
+      <c r="M6" t="n" s="0">
+        <v>9.85773E7</v>
+      </c>
+      <c r="N6" t="n" s="0">
+        <v>1.009569E8</v>
+      </c>
+      <c r="O6" t="n" s="0">
+        <v>1.009347E8</v>
+      </c>
+      <c r="P6" t="n" s="0">
+        <v>9.91675E7</v>
+      </c>
+      <c r="Q6" t="n" s="0">
+        <v>1.017983E8</v>
+      </c>
+      <c r="R6" t="n" s="0">
+        <v>1.326853E8</v>
+      </c>
+      <c r="S6" t="n" s="0">
+        <v>9.8944E7</v>
+      </c>
+      <c r="T6" t="n" s="0">
+        <v>1.006255E8</v>
+      </c>
+      <c r="U6" t="n" s="0">
+        <v>9.99287E7</v>
+      </c>
+      <c r="V6" t="n" s="0">
+        <v>9.8678E7</v>
+      </c>
+      <c r="W6" t="n" s="0">
+        <v>9.83971E7</v>
+      </c>
+      <c r="X6" t="n" s="0">
+        <v>9.90059E7</v>
+      </c>
+      <c r="Y6" t="n" s="0">
+        <v>9.94141E7</v>
+      </c>
+      <c r="Z6" t="n" s="0">
+        <v>9.82084E7</v>
+      </c>
+      <c r="AA6" t="n" s="0">
+        <v>9.91131E7</v>
+      </c>
+      <c r="AB6" t="n" s="0">
+        <v>9.9549E7</v>
+      </c>
+      <c r="AC6" t="n" s="0">
+        <v>9.93185E7</v>
+      </c>
+      <c r="AD6" t="n" s="0">
+        <v>9.87257E7</v>
+      </c>
+      <c r="AE6" t="n" s="0">
+        <v>9.95242E7</v>
+      </c>
+      <c r="AF6" t="n" s="0">
+        <v>9.93259E7</v>
+      </c>
+      <c r="AG6" t="n" s="0">
+        <v>1.002685E8</v>
+      </c>
+      <c r="AH6" t="n" s="0">
+        <v>1.07449E8</v>
+      </c>
+      <c r="AI6" t="n" s="0">
+        <v>1.06455E8</v>
+      </c>
+      <c r="AJ6" t="n" s="0">
+        <v>1.006364E8</v>
+      </c>
+      <c r="AK6" t="n" s="0">
+        <v>1.001837E8</v>
+      </c>
+      <c r="AL6" t="n" s="0">
+        <v>1.009337E8</v>
+      </c>
+      <c r="AM6" t="n" s="0">
+        <v>9.86068E7</v>
+      </c>
+      <c r="AN6" t="n" s="0">
+        <v>1.020207E8</v>
+      </c>
+      <c r="AO6" t="n" s="0">
+        <v>1.007386E8</v>
+      </c>
+      <c r="AP6" t="n" s="0">
+        <v>9.91582E7</v>
+      </c>
+      <c r="AQ6" t="n" s="0">
+        <v>9.88376E7</v>
+      </c>
+      <c r="AR6" t="n" s="0">
+        <v>9.96393E7</v>
+      </c>
+      <c r="AS6" t="n" s="0">
+        <v>9.91981E7</v>
+      </c>
+      <c r="AT6" t="n" s="0">
+        <v>9.86399E7</v>
+      </c>
+      <c r="AU6" t="n" s="0">
+        <v>9.83774E7</v>
+      </c>
+      <c r="AV6" t="n" s="0">
+        <v>9.88717E7</v>
+      </c>
+      <c r="AW6" t="n" s="0">
+        <v>9.86336E7</v>
+      </c>
+      <c r="AX6" t="n" s="0">
+        <v>9.86111E7</v>
+      </c>
+      <c r="AY6" t="n" s="0">
+        <v>9.91582E7</v>
+      </c>
+      <c r="AZ6" t="n" s="0">
+        <v>9.8994E7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B7" t="n" s="0">
+        <v>25000.0</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>1.618492E8</v>
+      </c>
+      <c r="D7" t="n" s="0">
+        <v>1.913223E8</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>9.89749E7</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>9.87799E7</v>
+      </c>
+      <c r="G7" t="n" s="0">
+        <v>9.89064E7</v>
+      </c>
+      <c r="H7" t="n" s="0">
+        <v>1.026327E8</v>
+      </c>
+      <c r="I7" t="n" s="0">
+        <v>9.95593E7</v>
+      </c>
+      <c r="J7" t="n" s="0">
+        <v>9.92948E7</v>
+      </c>
+      <c r="K7" t="n" s="0">
+        <v>1.02286E8</v>
+      </c>
+      <c r="L7" t="n" s="0">
+        <v>9.9073E7</v>
+      </c>
+      <c r="M7" t="n" s="0">
+        <v>1.324882E8</v>
+      </c>
+      <c r="N7" t="n" s="0">
+        <v>9.95171E7</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>1.020436E8</v>
+      </c>
+      <c r="P7" t="n" s="0">
+        <v>9.90205E7</v>
+      </c>
+      <c r="Q7" t="n" s="0">
+        <v>1.017398E8</v>
+      </c>
+      <c r="R7" t="n" s="0">
+        <v>1.008635E8</v>
+      </c>
+      <c r="S7" t="n" s="0">
+        <v>1.027056E8</v>
+      </c>
+      <c r="T7" t="n" s="0">
+        <v>9.89481E7</v>
+      </c>
+      <c r="U7" t="n" s="0">
+        <v>9.9383E7</v>
+      </c>
+      <c r="V7" t="n" s="0">
+        <v>9.95929E7</v>
+      </c>
+      <c r="W7" t="n" s="0">
+        <v>9.87361E7</v>
+      </c>
+      <c r="X7" t="n" s="0">
+        <v>9.96833E7</v>
+      </c>
+      <c r="Y7" t="n" s="0">
+        <v>1.003697E8</v>
+      </c>
+      <c r="Z7" t="n" s="0">
+        <v>9.87363E7</v>
+      </c>
+      <c r="AA7" t="n" s="0">
+        <v>1.011754E8</v>
+      </c>
+      <c r="AB7" t="n" s="0">
+        <v>9.88611E7</v>
+      </c>
+      <c r="AC7" t="n" s="0">
+        <v>9.85617E7</v>
+      </c>
+      <c r="AD7" t="n" s="0">
+        <v>9.88168E7</v>
+      </c>
+      <c r="AE7" t="n" s="0">
+        <v>9.89617E7</v>
+      </c>
+      <c r="AF7" t="n" s="0">
+        <v>9.95533E7</v>
+      </c>
+      <c r="AG7" t="n" s="0">
+        <v>1.00302E8</v>
+      </c>
+      <c r="AH7" t="n" s="0">
+        <v>1.071377E8</v>
+      </c>
+      <c r="AI7" t="n" s="0">
+        <v>1.068535E8</v>
+      </c>
+      <c r="AJ7" t="n" s="0">
+        <v>9.91618E7</v>
+      </c>
+      <c r="AK7" t="n" s="0">
+        <v>9.97696E7</v>
+      </c>
+      <c r="AL7" t="n" s="0">
+        <v>1.007217E8</v>
+      </c>
+      <c r="AM7" t="n" s="0">
+        <v>1.003364E8</v>
+      </c>
+      <c r="AN7" t="n" s="0">
+        <v>1.021224E8</v>
+      </c>
+      <c r="AO7" t="n" s="0">
+        <v>1.010553E8</v>
+      </c>
+      <c r="AP7" t="n" s="0">
+        <v>9.89789E7</v>
+      </c>
+      <c r="AQ7" t="n" s="0">
+        <v>9.98589E7</v>
+      </c>
+      <c r="AR7" t="n" s="0">
+        <v>1.006828E8</v>
+      </c>
+      <c r="AS7" t="n" s="0">
+        <v>9.85888E7</v>
+      </c>
+      <c r="AT7" t="n" s="0">
+        <v>9.90278E7</v>
+      </c>
+      <c r="AU7" t="n" s="0">
+        <v>9.87595E7</v>
+      </c>
+      <c r="AV7" t="n" s="0">
+        <v>9.89187E7</v>
+      </c>
+      <c r="AW7" t="n" s="0">
+        <v>9.96409E7</v>
+      </c>
+      <c r="AX7" t="n" s="0">
+        <v>1.002653E8</v>
+      </c>
+      <c r="AY7" t="n" s="0">
+        <v>1.017115E8</v>
+      </c>
+      <c r="AZ7" t="n" s="0">
+        <v>9.96454E7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B8" t="n" s="0">
+        <v>25000.0</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>4498500.0</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>2174800.0</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>2443900.0</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>2073500.0</v>
+      </c>
+      <c r="G8" t="n" s="0">
+        <v>2526400.0</v>
+      </c>
+      <c r="H8" t="n" s="0">
+        <v>2700800.0</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>2041100.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>2222200.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>2021700.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>2511000.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>2116200.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>2250600.0</v>
+      </c>
+      <c r="O8" t="n" s="0">
+        <v>2089500.0</v>
+      </c>
+      <c r="P8" t="n" s="0">
+        <v>2445000.0</v>
+      </c>
+      <c r="Q8" t="n" s="0">
+        <v>2438700.0</v>
+      </c>
+      <c r="R8" t="n" s="0">
+        <v>2457300.0</v>
+      </c>
+      <c r="S8" t="n" s="0">
+        <v>2563100.0</v>
+      </c>
+      <c r="T8" t="n" s="0">
+        <v>2367100.0</v>
+      </c>
+      <c r="U8" t="n" s="0">
+        <v>2015500.0</v>
+      </c>
+      <c r="V8" t="n" s="0">
+        <v>2471500.0</v>
+      </c>
+      <c r="W8" t="n" s="0">
+        <v>2516100.0</v>
+      </c>
+      <c r="X8" t="n" s="0">
+        <v>2252000.0</v>
+      </c>
+      <c r="Y8" t="n" s="0">
+        <v>2427100.0</v>
+      </c>
+      <c r="Z8" t="n" s="0">
+        <v>2451900.0</v>
+      </c>
+      <c r="AA8" t="n" s="0">
+        <v>2110300.0</v>
+      </c>
+      <c r="AB8" t="n" s="0">
+        <v>2465300.0</v>
+      </c>
+      <c r="AC8" t="n" s="0">
+        <v>2441200.0</v>
+      </c>
+      <c r="AD8" t="n" s="0">
+        <v>2046900.0</v>
+      </c>
+      <c r="AE8" t="n" s="0">
+        <v>2283100.0</v>
+      </c>
+      <c r="AF8" t="n" s="0">
+        <v>2447200.0</v>
+      </c>
+      <c r="AG8" t="n" s="0">
+        <v>2457800.0</v>
+      </c>
+      <c r="AH8" t="n" s="0">
+        <v>2211300.0</v>
+      </c>
+      <c r="AI8" t="n" s="0">
+        <v>2355700.0</v>
+      </c>
+      <c r="AJ8" t="n" s="0">
+        <v>2483800.0</v>
+      </c>
+      <c r="AK8" t="n" s="0">
+        <v>2440900.0</v>
+      </c>
+      <c r="AL8" t="n" s="0">
+        <v>2225600.0</v>
+      </c>
+      <c r="AM8" t="n" s="0">
+        <v>2041300.0</v>
+      </c>
+      <c r="AN8" t="n" s="0">
+        <v>2068700.0</v>
+      </c>
+      <c r="AO8" t="n" s="0">
+        <v>2488300.0</v>
+      </c>
+      <c r="AP8" t="n" s="0">
+        <v>2543000.0</v>
+      </c>
+      <c r="AQ8" t="n" s="0">
+        <v>2472300.0</v>
+      </c>
+      <c r="AR8" t="n" s="0">
+        <v>2059400.0</v>
+      </c>
+      <c r="AS8" t="n" s="0">
+        <v>2020900.0</v>
+      </c>
+      <c r="AT8" t="n" s="0">
+        <v>2445400.0</v>
+      </c>
+      <c r="AU8" t="n" s="0">
+        <v>2591500.0</v>
+      </c>
+      <c r="AV8" t="n" s="0">
+        <v>9.40044E7</v>
+      </c>
+      <c r="AW8" t="n" s="0">
+        <v>2123800.0</v>
+      </c>
+      <c r="AX8" t="n" s="0">
+        <v>2261600.0</v>
+      </c>
+      <c r="AY8" t="n" s="0">
+        <v>2037900.0</v>
+      </c>
+      <c r="AZ8" t="n" s="0">
+        <v>2484600.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B9" t="n" s="0">
+        <v>25000.0</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>4007000.0</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>2579600.0</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>2560800.0</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>2087700.0</v>
+      </c>
+      <c r="G9" t="n" s="0">
+        <v>2657100.0</v>
+      </c>
+      <c r="H9" t="n" s="0">
+        <v>2662900.0</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>2093600.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>2119200.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>2011300.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>2483600.0</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>2130700.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>2059300.0</v>
+      </c>
+      <c r="O9" t="n" s="0">
+        <v>2055300.0</v>
+      </c>
+      <c r="P9" t="n" s="0">
+        <v>2480700.0</v>
+      </c>
+      <c r="Q9" t="n" s="0">
+        <v>2594700.0</v>
+      </c>
+      <c r="R9" t="n" s="0">
+        <v>2454900.0</v>
+      </c>
+      <c r="S9" t="n" s="0">
+        <v>2189400.0</v>
+      </c>
+      <c r="T9" t="n" s="0">
+        <v>2518600.0</v>
+      </c>
+      <c r="U9" t="n" s="0">
+        <v>2042700.0</v>
+      </c>
+      <c r="V9" t="n" s="0">
+        <v>2472000.0</v>
+      </c>
+      <c r="W9" t="n" s="0">
+        <v>5.47293E7</v>
+      </c>
+      <c r="X9" t="n" s="0">
+        <v>2047500.0</v>
+      </c>
+      <c r="Y9" t="n" s="0">
+        <v>2509400.0</v>
+      </c>
+      <c r="Z9" t="n" s="0">
+        <v>2489600.0</v>
+      </c>
+      <c r="AA9" t="n" s="0">
+        <v>2092100.0</v>
+      </c>
+      <c r="AB9" t="n" s="0">
+        <v>2856500.0</v>
+      </c>
+      <c r="AC9" t="n" s="0">
+        <v>2502500.0</v>
+      </c>
+      <c r="AD9" t="n" s="0">
+        <v>2179600.0</v>
+      </c>
+      <c r="AE9" t="n" s="0">
+        <v>2211100.0</v>
+      </c>
+      <c r="AF9" t="n" s="0">
+        <v>2456300.0</v>
+      </c>
+      <c r="AG9" t="n" s="0">
+        <v>2550700.0</v>
+      </c>
+      <c r="AH9" t="n" s="0">
+        <v>2241200.0</v>
+      </c>
+      <c r="AI9" t="n" s="0">
+        <v>2601200.0</v>
+      </c>
+      <c r="AJ9" t="n" s="0">
+        <v>2490400.0</v>
+      </c>
+      <c r="AK9" t="n" s="0">
+        <v>2762600.0</v>
+      </c>
+      <c r="AL9" t="n" s="0">
+        <v>2290200.0</v>
+      </c>
+      <c r="AM9" t="n" s="0">
+        <v>2002600.0</v>
+      </c>
+      <c r="AN9" t="n" s="0">
+        <v>2048400.0</v>
+      </c>
+      <c r="AO9" t="n" s="0">
+        <v>2605100.0</v>
+      </c>
+      <c r="AP9" t="n" s="0">
+        <v>2486400.0</v>
+      </c>
+      <c r="AQ9" t="n" s="0">
+        <v>2431000.0</v>
+      </c>
+      <c r="AR9" t="n" s="0">
+        <v>2136900.0</v>
+      </c>
+      <c r="AS9" t="n" s="0">
+        <v>1998300.0</v>
+      </c>
+      <c r="AT9" t="n" s="0">
+        <v>2459700.0</v>
+      </c>
+      <c r="AU9" t="n" s="0">
+        <v>2483400.0</v>
+      </c>
+      <c r="AV9" t="n" s="0">
+        <v>2288200.0</v>
+      </c>
+      <c r="AW9" t="n" s="0">
+        <v>2061700.0</v>
+      </c>
+      <c r="AX9" t="n" s="0">
+        <v>2588400.0</v>
+      </c>
+      <c r="AY9" t="n" s="0">
+        <v>2102000.0</v>
+      </c>
+      <c r="AZ9" t="n" s="0">
+        <v>2534100.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B10" t="n" s="0">
+        <v>25000.0</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>6282900.0</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>3179200.0</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>3071700.0</v>
+      </c>
+      <c r="F10" t="n" s="0">
+        <v>2.38199E7</v>
+      </c>
+      <c r="G10" t="n" s="0">
+        <v>3277900.0</v>
+      </c>
+      <c r="H10" t="n" s="0">
+        <v>3128500.0</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>2410900.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>2379100.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>2359700.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>2996200.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>2.50543E7</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>2338400.0</v>
+      </c>
+      <c r="O10" t="n" s="0">
+        <v>2421700.0</v>
+      </c>
+      <c r="P10" t="n" s="0">
+        <v>3222800.0</v>
+      </c>
+      <c r="Q10" t="n" s="0">
+        <v>3340700.0</v>
+      </c>
+      <c r="R10" t="n" s="0">
+        <v>5.06835E7</v>
+      </c>
+      <c r="S10" t="n" s="0">
+        <v>2382100.0</v>
+      </c>
+      <c r="T10" t="n" s="0">
+        <v>3062600.0</v>
+      </c>
+      <c r="U10" t="n" s="0">
+        <v>2465300.0</v>
+      </c>
+      <c r="V10" t="n" s="0">
+        <v>3146200.0</v>
+      </c>
+      <c r="W10" t="n" s="0">
+        <v>2688000.0</v>
+      </c>
+      <c r="X10" t="n" s="0">
+        <v>2336600.0</v>
+      </c>
+      <c r="Y10" t="n" s="0">
+        <v>3143700.0</v>
+      </c>
+      <c r="Z10" t="n" s="0">
+        <v>3250600.0</v>
+      </c>
+      <c r="AA10" t="n" s="0">
+        <v>2547200.0</v>
+      </c>
+      <c r="AB10" t="n" s="0">
+        <v>3328700.0</v>
+      </c>
+      <c r="AC10" t="n" s="0">
+        <v>2991600.0</v>
+      </c>
+      <c r="AD10" t="n" s="0">
+        <v>2496300.0</v>
+      </c>
+      <c r="AE10" t="n" s="0">
+        <v>2376800.0</v>
+      </c>
+      <c r="AF10" t="n" s="0">
+        <v>3077900.0</v>
+      </c>
+      <c r="AG10" t="n" s="0">
+        <v>3105800.0</v>
+      </c>
+      <c r="AH10" t="n" s="0">
+        <v>2653700.0</v>
+      </c>
+      <c r="AI10" t="n" s="0">
+        <v>2637600.0</v>
+      </c>
+      <c r="AJ10" t="n" s="0">
+        <v>3298700.0</v>
+      </c>
+      <c r="AK10" t="n" s="0">
+        <v>3410400.0</v>
+      </c>
+      <c r="AL10" t="n" s="0">
+        <v>2505700.0</v>
+      </c>
+      <c r="AM10" t="n" s="0">
+        <v>2532200.0</v>
+      </c>
+      <c r="AN10" t="n" s="0">
+        <v>2423500.0</v>
+      </c>
+      <c r="AO10" t="n" s="0">
+        <v>3130800.0</v>
+      </c>
+      <c r="AP10" t="n" s="0">
+        <v>3590000.0</v>
+      </c>
+      <c r="AQ10" t="n" s="0">
+        <v>3087300.0</v>
+      </c>
+      <c r="AR10" t="n" s="0">
+        <v>2554600.0</v>
+      </c>
+      <c r="AS10" t="n" s="0">
+        <v>2450000.0</v>
+      </c>
+      <c r="AT10" t="n" s="0">
+        <v>3039000.0</v>
+      </c>
+      <c r="AU10" t="n" s="0">
+        <v>3478600.0</v>
+      </c>
+      <c r="AV10" t="n" s="0">
+        <v>2496500.0</v>
+      </c>
+      <c r="AW10" t="n" s="0">
+        <v>2512400.0</v>
+      </c>
+      <c r="AX10" t="n" s="0">
+        <v>2492600.0</v>
+      </c>
+      <c r="AY10" t="n" s="0">
+        <v>2332900.0</v>
+      </c>
+      <c r="AZ10" t="n" s="0">
+        <v>3251300.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B11" t="n" s="0">
+        <v>25000.0</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>2.04987E7</v>
+      </c>
+      <c r="D11" t="n" s="0">
+        <v>3100300.0</v>
+      </c>
+      <c r="E11" t="n" s="0">
+        <v>8319500.0</v>
+      </c>
+      <c r="F11" t="n" s="0">
+        <v>3225000.0</v>
+      </c>
+      <c r="G11" t="n" s="0">
+        <v>3145500.0</v>
+      </c>
+      <c r="H11" t="n" s="0">
+        <v>3024300.0</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>2271900.0</v>
+      </c>
+      <c r="J11" t="n" s="0">
+        <v>2397600.0</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>2783700.0</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>2638600.0</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>2506400.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>2810600.0</v>
+      </c>
+      <c r="O11" t="n" s="0">
+        <v>2771200.0</v>
+      </c>
+      <c r="P11" t="n" s="0">
+        <v>2948200.0</v>
+      </c>
+      <c r="Q11" t="n" s="0">
+        <v>3051600.0</v>
+      </c>
+      <c r="R11" t="n" s="0">
+        <v>2599600.0</v>
+      </c>
+      <c r="S11" t="n" s="0">
+        <v>2449100.0</v>
+      </c>
+      <c r="T11" t="n" s="0">
+        <v>3093000.0</v>
+      </c>
+      <c r="U11" t="n" s="0">
+        <v>2536300.0</v>
+      </c>
+      <c r="V11" t="n" s="0">
+        <v>3192700.0</v>
+      </c>
+      <c r="W11" t="n" s="0">
+        <v>2447600.0</v>
+      </c>
+      <c r="X11" t="n" s="0">
+        <v>2819100.0</v>
+      </c>
+      <c r="Y11" t="n" s="0">
+        <v>3059400.0</v>
+      </c>
+      <c r="Z11" t="n" s="0">
+        <v>3206900.0</v>
+      </c>
+      <c r="AA11" t="n" s="0">
+        <v>2384400.0</v>
+      </c>
+      <c r="AB11" t="n" s="0">
+        <v>3232000.0</v>
+      </c>
+      <c r="AC11" t="n" s="0">
+        <v>2976100.0</v>
+      </c>
+      <c r="AD11" t="n" s="0">
+        <v>2288500.0</v>
+      </c>
+      <c r="AE11" t="n" s="0">
+        <v>2663200.0</v>
+      </c>
+      <c r="AF11" t="n" s="0">
+        <v>3096000.0</v>
+      </c>
+      <c r="AG11" t="n" s="0">
+        <v>3140100.0</v>
+      </c>
+      <c r="AH11" t="n" s="0">
+        <v>3115900.0</v>
+      </c>
+      <c r="AI11" t="n" s="0">
+        <v>2901100.0</v>
+      </c>
+      <c r="AJ11" t="n" s="0">
+        <v>3036900.0</v>
+      </c>
+      <c r="AK11" t="n" s="0">
+        <v>3180700.0</v>
+      </c>
+      <c r="AL11" t="n" s="0">
+        <v>3006600.0</v>
+      </c>
+      <c r="AM11" t="n" s="0">
+        <v>2499800.0</v>
+      </c>
+      <c r="AN11" t="n" s="0">
+        <v>2666500.0</v>
+      </c>
+      <c r="AO11" t="n" s="0">
+        <v>3163700.0</v>
+      </c>
+      <c r="AP11" t="n" s="0">
+        <v>3033400.0</v>
+      </c>
+      <c r="AQ11" t="n" s="0">
+        <v>3023100.0</v>
+      </c>
+      <c r="AR11" t="n" s="0">
+        <v>2375500.0</v>
+      </c>
+      <c r="AS11" t="n" s="0">
+        <v>2277100.0</v>
+      </c>
+      <c r="AT11" t="n" s="0">
+        <v>2984700.0</v>
+      </c>
+      <c r="AU11" t="n" s="0">
+        <v>3038800.0</v>
+      </c>
+      <c r="AV11" t="n" s="0">
+        <v>2410800.0</v>
+      </c>
+      <c r="AW11" t="n" s="0">
+        <v>2830500.0</v>
+      </c>
+      <c r="AX11" t="n" s="0">
+        <v>2307600.0</v>
+      </c>
+      <c r="AY11" t="n" s="0">
+        <v>2443100.0</v>
+      </c>
+      <c r="AZ11" t="n" s="0">
+        <v>3069100.0</v>
       </c>
     </row>
   </sheetData>
